--- a/reports/selenium/Excel/Web_Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Web_Automation_Test_Report.xlsx
@@ -538,7 +538,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>URL:   |  Date: 2026-06-23 08:05 UTC  |  Total: 153  |  Passed: 102  |  Failed: 51</t>
+          <t>URL:   |  Date: 2026-06-23 09:03 UTC  |  Total: 153  |  Passed: 102  |  Failed: 51</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>13.96</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>40.72</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>56.24</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>53.59</t>
+          <t>53.76</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr"/>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>41.10</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>66.82</t>
+          <t>66.89</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr"/>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr"/>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>29.50</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.69</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>29.93</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>33.11</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr"/>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr"/>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr"/>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr"/>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr"/>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr"/>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr"/>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr"/>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.08</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr"/>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.80</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr"/>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:05 UTC</t>
+          <t>2026-06-23 09:03 UTC</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
